--- a/Employee task5_Details.xlsx
+++ b/Employee task5_Details.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAJASHREE KANNAYERAM\Documents\jaya project in excel\EXCEL CODING CHALLANGE IN GITHUB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126A03C3-897C-418D-8043-7971D28DE92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364969CF-EA1D-406D-B813-03D8270D887F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="table1" sheetId="1" r:id="rId1"/>
-    <sheet name="observation " sheetId="3" r:id="rId2"/>
+    <sheet name="observation5" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -899,9 +899,6 @@
     <t>user30@example.com</t>
   </si>
   <si>
-    <t>observation</t>
-  </si>
-  <si>
     <t>LEFT</t>
   </si>
   <si>
@@ -1055,6 +1052,9 @@
       <t xml:space="preserve"> These functions helped format and organize employee names easily.</t>
     </r>
   </si>
+  <si>
+    <t>OBSERVATION</t>
+  </si>
 </sst>
 </file>
 
@@ -1063,7 +1063,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1100,8 +1100,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1138,6 +1146,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1166,7 +1180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1198,10 +1212,11 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -1210,26 +1225,11 @@
   </cellStyles>
   <dxfs count="13">
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FF240B7F"/>
+          <bgColor theme="4" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1240,8 +1240,12 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top/>
-        <bottom/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
         <vertical style="thin">
           <color indexed="64"/>
         </vertical>
@@ -1307,36 +1311,6 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1531,12 +1505,54 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF240B7F"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{99D76C34-85D6-4717-BA7F-5953D1A75D86}"/>
   </tableStyles>
   <colors>
     <mruColors>
+      <color rgb="FFFEF8D6"/>
       <color rgb="FF240B7F"/>
       <color rgb="FFFF9933"/>
       <color rgb="FF0D41E9"/>
@@ -1559,15 +1575,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E2277F7-B24A-4B9E-AC8D-2890DA48D9BC}" name="Table1" displayName="Table1" ref="A1:I151" totalsRowShown="0" headerRowDxfId="0" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E2277F7-B24A-4B9E-AC8D-2890DA48D9BC}" name="Table1" displayName="Table1" ref="A1:I151" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9">
   <autoFilter ref="A1:I151" xr:uid="{4E2277F7-B24A-4B9E-AC8D-2890DA48D9BC}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{B746C748-5141-4287-8FBE-14ED18C42139}" name="Employee ID" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{1C379FDD-99E6-4964-91E4-AD5BEA4988C7}" name="Name" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{E8B9EFDF-4BB0-40A2-B2CF-EEBF3C145F79}" name="Department" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{3611A9C0-49E3-4348-8153-44C4AF5A9437}" name="Country" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{45954127-FDD3-4B20-AD44-20A887EC5B47}" name="Salary" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{BE88C9D1-550A-4E8E-8505-EF96BF3FD42F}" name="Date of Joining" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{B746C748-5141-4287-8FBE-14ED18C42139}" name="Employee ID" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{1C379FDD-99E6-4964-91E4-AD5BEA4988C7}" name="Name" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{E8B9EFDF-4BB0-40A2-B2CF-EEBF3C145F79}" name="Department" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{3611A9C0-49E3-4348-8153-44C4AF5A9437}" name="Country" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{45954127-FDD3-4B20-AD44-20A887EC5B47}" name="Salary" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{BE88C9D1-550A-4E8E-8505-EF96BF3FD42F}" name="Date of Joining" dataDxfId="0"/>
     <tableColumn id="7" xr3:uid="{8EE82193-638D-4802-8BE7-F1AF2D9A40F5}" name="Performance Rating" dataDxfId="3"/>
     <tableColumn id="8" xr3:uid="{1E7D60E1-3991-4687-B63F-2AF44EFB60EF}" name="Gender" dataDxfId="2"/>
     <tableColumn id="9" xr3:uid="{37265619-7A41-4865-9FC0-5E9A3BA6C689}" name="Email" dataDxfId="1"/>
@@ -1914,22 +1930,22 @@
         <v>8</v>
       </c>
       <c r="K1" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="L1" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="P1" s="10" t="s">
         <v>286</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
@@ -8721,52 +8737,52 @@
   <dimension ref="C3:C26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="223.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C3" t="s">
-        <v>281</v>
+      <c r="C3" s="11" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="12" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C5" s="12" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="5" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C5" s="11" t="s">
+    <row r="6" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C6" s="12" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C6" s="11" t="s">
+    <row r="7" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C7" s="12" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C7" s="11" t="s">
+    <row r="8" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C8" s="12" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="8" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C8" s="11" t="s">
+    <row r="9" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C9" s="12" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="9" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C9" s="11" t="s">
+    <row r="10" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C10" s="13" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="11" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C11" s="13" t="s">
         <v>293</v>
-      </c>
-    </row>
-    <row r="10" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C10" s="12" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="11" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C11" s="12" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="26" spans="3:3" x14ac:dyDescent="0.3">
